--- a/Result/30-05-25/NASDAQstock_30-05-25period252RS90.xlsx
+++ b/Result/30-05-25/NASDAQstock_30-05-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/30-05-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F83F7C2-D961-1843-A9CE-6D87D27C9A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE822446-D77F-FE4E-8B0A-971402457FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -898,6 +898,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
@@ -909,13 +916,6 @@
       <name val="新細明體"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -923,6 +923,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -940,12 +946,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -990,14 +990,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1432,7 +1432,7 @@
       </c>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B2">
@@ -1492,7 +1492,7 @@
       <c r="U2">
         <v>8.8888888888888875</v>
       </c>
-      <c r="V2" s="2" t="b">
+      <c r="V2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="b">
@@ -1534,7 +1534,7 @@
       <c r="AI2" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK2" t="s">
@@ -1659,7 +1659,7 @@
       <c r="AI3" t="s">
         <v>49</v>
       </c>
-      <c r="AJ3" s="4" t="s">
+      <c r="AJ3" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK3" t="s">
@@ -1784,7 +1784,7 @@
       <c r="AI4" t="s">
         <v>53</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AJ4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK4" t="s">
@@ -1807,7 +1807,7 @@
       </c>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B5">
@@ -1867,7 +1867,7 @@
       <c r="U5">
         <v>16.111111111111111</v>
       </c>
-      <c r="V5" s="2" t="b">
+      <c r="V5" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="b">
@@ -1909,7 +1909,7 @@
       <c r="AI5" t="s">
         <v>56</v>
       </c>
-      <c r="AJ5" s="3" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK5" t="s">
@@ -1932,7 +1932,7 @@
       </c>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B6">
@@ -2034,7 +2034,7 @@
       <c r="AI6" t="s">
         <v>43</v>
       </c>
-      <c r="AJ6" s="3" t="s">
+      <c r="AJ6" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK6" t="s">
@@ -2057,7 +2057,7 @@
       </c>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B7">
@@ -2159,7 +2159,7 @@
       <c r="AI7" t="s">
         <v>49</v>
       </c>
-      <c r="AJ7" s="4" t="s">
+      <c r="AJ7" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK7" t="s">
@@ -2284,7 +2284,7 @@
       <c r="AI8" t="s">
         <v>43</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AJ8" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK8" t="s">
@@ -2409,7 +2409,7 @@
       <c r="AI9" t="s">
         <v>67</v>
       </c>
-      <c r="AJ9" s="4" t="s">
+      <c r="AJ9" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK9" t="s">
@@ -2534,7 +2534,7 @@
       <c r="AI10" t="s">
         <v>71</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AJ10" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK10" t="s">
@@ -2659,7 +2659,7 @@
       <c r="AI11" t="s">
         <v>74</v>
       </c>
-      <c r="AJ11" s="3" t="s">
+      <c r="AJ11" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK11" t="s">
@@ -2682,7 +2682,7 @@
       </c>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B12">
@@ -2742,7 +2742,7 @@
       <c r="U12">
         <v>2.2222222222222219</v>
       </c>
-      <c r="V12" s="2" t="b">
+      <c r="V12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="b">
@@ -2784,7 +2784,7 @@
       <c r="AI12" t="s">
         <v>49</v>
       </c>
-      <c r="AJ12" s="4" t="s">
+      <c r="AJ12" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK12" t="s">
@@ -2909,7 +2909,7 @@
       <c r="AI13" t="s">
         <v>81</v>
       </c>
-      <c r="AJ13" s="4" t="s">
+      <c r="AJ13" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK13" t="s">
@@ -3034,7 +3034,7 @@
       <c r="AI14" t="s">
         <v>84</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK14" t="s">
@@ -3057,7 +3057,7 @@
       </c>
     </row>
     <row r="15" spans="1:42">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B15">
@@ -3159,7 +3159,7 @@
       <c r="AI15" t="s">
         <v>87</v>
       </c>
-      <c r="AJ15" s="4" t="s">
+      <c r="AJ15" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK15" t="s">
@@ -3182,7 +3182,7 @@
       </c>
     </row>
     <row r="16" spans="1:42">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B16">
@@ -3284,7 +3284,7 @@
       <c r="AI16" t="s">
         <v>90</v>
       </c>
-      <c r="AJ16" s="4" t="s">
+      <c r="AJ16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK16" t="s">
@@ -3307,7 +3307,7 @@
       </c>
     </row>
     <row r="17" spans="1:42">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B17">
@@ -3409,7 +3409,7 @@
       <c r="AI17" t="s">
         <v>44</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AJ17" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK17" t="s">
@@ -3492,7 +3492,7 @@
       <c r="U18">
         <v>16.666666666666661</v>
       </c>
-      <c r="V18" s="2" t="b">
+      <c r="V18" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="b">
@@ -3534,7 +3534,7 @@
       <c r="AI18" t="s">
         <v>95</v>
       </c>
-      <c r="AJ18" s="4" t="s">
+      <c r="AJ18" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK18" t="s">
@@ -3617,7 +3617,7 @@
       <c r="U19">
         <v>11.111111111111111</v>
       </c>
-      <c r="V19" s="2" t="b">
+      <c r="V19" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="b">
@@ -3659,7 +3659,7 @@
       <c r="AI19" t="s">
         <v>44</v>
       </c>
-      <c r="AJ19" s="4" t="s">
+      <c r="AJ19" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK19" t="s">
@@ -3682,7 +3682,7 @@
       </c>
     </row>
     <row r="20" spans="1:42">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B20">
@@ -3784,7 +3784,7 @@
       <c r="AI20" t="s">
         <v>74</v>
       </c>
-      <c r="AJ20" s="4" t="s">
+      <c r="AJ20" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK20" t="s">
@@ -3909,7 +3909,7 @@
       <c r="AI21" t="s">
         <v>95</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AJ21" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK21" t="s">
@@ -4034,7 +4034,7 @@
       <c r="AI22" t="s">
         <v>49</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AJ22" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK22" t="s">
@@ -4057,7 +4057,7 @@
       </c>
     </row>
     <row r="23" spans="1:42">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B23">
@@ -4159,7 +4159,7 @@
       <c r="AI23" t="s">
         <v>102</v>
       </c>
-      <c r="AJ23" s="4" t="s">
+      <c r="AJ23" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK23" t="s">
@@ -4182,7 +4182,7 @@
       </c>
     </row>
     <row r="24" spans="1:42">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B24">
@@ -4242,7 +4242,7 @@
       <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="b">
+      <c r="V24" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W24" t="b">
@@ -4284,7 +4284,7 @@
       <c r="AI24" t="s">
         <v>102</v>
       </c>
-      <c r="AJ24" s="3" t="s">
+      <c r="AJ24" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK24" t="s">
@@ -4307,7 +4307,7 @@
       </c>
     </row>
     <row r="25" spans="1:42">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B25">
@@ -4364,7 +4364,7 @@
       <c r="S25">
         <v>1.1299999999999999</v>
       </c>
-      <c r="T25" s="5" t="s">
+      <c r="T25" s="6" t="s">
         <v>19</v>
       </c>
       <c r="U25">
@@ -4412,7 +4412,7 @@
       <c r="AI25" t="s">
         <v>84</v>
       </c>
-      <c r="AJ25" s="4" t="s">
+      <c r="AJ25" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK25" t="s">
@@ -4537,7 +4537,7 @@
       <c r="AI26" t="s">
         <v>84</v>
       </c>
-      <c r="AJ26" s="4" t="s">
+      <c r="AJ26" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK26" t="s">
@@ -4620,7 +4620,7 @@
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="b">
+      <c r="V27" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W27" t="b">
@@ -4662,7 +4662,7 @@
       <c r="AI27" t="s">
         <v>44</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AJ27" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK27" t="s">
@@ -4685,7 +4685,7 @@
       </c>
     </row>
     <row r="28" spans="1:42">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B28">
@@ -4745,7 +4745,7 @@
       <c r="U28">
         <v>19.44444444444445</v>
       </c>
-      <c r="V28" s="2" t="b">
+      <c r="V28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W28" t="b">
@@ -4787,7 +4787,7 @@
       <c r="AI28" t="s">
         <v>84</v>
       </c>
-      <c r="AJ28" s="3" t="s">
+      <c r="AJ28" s="4" t="s">
         <v>110</v>
       </c>
       <c r="AK28" t="s">
@@ -4810,7 +4810,7 @@
       </c>
     </row>
     <row r="29" spans="1:42">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>112</v>
       </c>
       <c r="B29">
@@ -4912,7 +4912,7 @@
       <c r="AI29" t="s">
         <v>113</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AJ29" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK29" t="s">
@@ -4935,7 +4935,7 @@
       </c>
     </row>
     <row r="30" spans="1:42">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B30">
@@ -4995,7 +4995,7 @@
       <c r="U30">
         <v>9.4444444444444429</v>
       </c>
-      <c r="V30" s="2" t="b">
+      <c r="V30" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W30" t="b">
@@ -5037,7 +5037,7 @@
       <c r="AI30" t="s">
         <v>116</v>
       </c>
-      <c r="AJ30" s="4" t="s">
+      <c r="AJ30" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK30" t="s">
@@ -5120,7 +5120,7 @@
       <c r="U31">
         <v>6.666666666666667</v>
       </c>
-      <c r="V31" s="2" t="b">
+      <c r="V31" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W31" t="b">
@@ -5162,7 +5162,7 @@
       <c r="AI31" t="s">
         <v>120</v>
       </c>
-      <c r="AJ31" s="4" t="s">
+      <c r="AJ31" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK31" t="s">
@@ -5287,7 +5287,7 @@
       <c r="AI32" t="s">
         <v>84</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AJ32" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK32" t="s">
@@ -5343,7 +5343,7 @@
       <c r="K33">
         <v>1.63</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L33" s="6">
         <v>-1.1587253668031761</v>
       </c>
       <c r="M33">
@@ -5370,7 +5370,7 @@
       <c r="U33">
         <v>11.111111111111111</v>
       </c>
-      <c r="V33" s="2" t="b">
+      <c r="V33" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W33" t="b">
@@ -5409,7 +5409,7 @@
       <c r="AI33" t="s">
         <v>90</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AJ33" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK33" t="s">
@@ -5465,7 +5465,7 @@
       <c r="K34">
         <v>1.68</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34" s="6">
         <v>-1.1310130166875489</v>
       </c>
       <c r="M34">
@@ -5492,7 +5492,7 @@
       <c r="U34">
         <v>0.55555555555555547</v>
       </c>
-      <c r="V34" s="2" t="b">
+      <c r="V34" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W34" t="b">
@@ -5534,7 +5534,7 @@
       <c r="AI34" t="s">
         <v>102</v>
       </c>
-      <c r="AJ34" s="4" t="s">
+      <c r="AJ34" s="5" t="s">
         <v>128</v>
       </c>
       <c r="AK34" t="s">
@@ -5617,7 +5617,7 @@
       <c r="U35">
         <v>0</v>
       </c>
-      <c r="V35" s="2" t="b">
+      <c r="V35" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W35" t="b">
@@ -5659,7 +5659,7 @@
       <c r="AI35" t="s">
         <v>102</v>
       </c>
-      <c r="AJ35" s="4" t="s">
+      <c r="AJ35" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK35" t="s">
@@ -5709,7 +5709,7 @@
       <c r="I36">
         <v>0.91</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="6">
         <v>-1.091973023771629</v>
       </c>
       <c r="K36">
@@ -5742,7 +5742,7 @@
       <c r="U36">
         <v>11.111111111111111</v>
       </c>
-      <c r="V36" s="2" t="b">
+      <c r="V36" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W36" t="b">
@@ -5784,7 +5784,7 @@
       <c r="AI36" t="s">
         <v>132</v>
       </c>
-      <c r="AJ36" s="4" t="s">
+      <c r="AJ36" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK36" t="s">
@@ -5807,7 +5807,7 @@
       </c>
     </row>
     <row r="37" spans="1:42">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>134</v>
       </c>
       <c r="B37">
@@ -5867,7 +5867,7 @@
       <c r="U37">
         <v>0</v>
       </c>
-      <c r="V37" s="2" t="b">
+      <c r="V37" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W37" t="b">
@@ -5909,7 +5909,7 @@
       <c r="AI37" t="s">
         <v>49</v>
       </c>
-      <c r="AJ37" s="4" t="s">
+      <c r="AJ37" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK37" t="s">
@@ -5932,7 +5932,7 @@
       </c>
     </row>
     <row r="38" spans="1:42">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B38">
@@ -5959,13 +5959,13 @@
       <c r="I38">
         <v>9.44</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="7">
         <v>2.8085324377887888</v>
       </c>
       <c r="K38">
         <v>8.48</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="7">
         <v>2.637866599037745</v>
       </c>
       <c r="M38">
@@ -6034,7 +6034,7 @@
       <c r="AI38" t="s">
         <v>84</v>
       </c>
-      <c r="AJ38" s="4" t="s">
+      <c r="AJ38" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK38" t="s">
@@ -6120,7 +6120,7 @@
       <c r="U39">
         <v>3.888888888888888</v>
       </c>
-      <c r="V39" s="2" t="b">
+      <c r="V39" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W39" t="b">
@@ -6162,7 +6162,7 @@
       <c r="AI39" t="s">
         <v>53</v>
       </c>
-      <c r="AJ39" s="4" t="s">
+      <c r="AJ39" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK39" t="s">
@@ -6212,7 +6212,7 @@
       <c r="I40">
         <v>1.05</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="6">
         <v>-1.027955349138751</v>
       </c>
       <c r="K40">
@@ -6248,7 +6248,7 @@
       <c r="U40">
         <v>5</v>
       </c>
-      <c r="V40" s="2" t="b">
+      <c r="V40" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W40" t="b">
@@ -6287,7 +6287,7 @@
       <c r="AI40" t="s">
         <v>44</v>
       </c>
-      <c r="AJ40" s="4" t="s">
+      <c r="AJ40" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK40" t="s">
@@ -6409,7 +6409,7 @@
       <c r="AI41" t="s">
         <v>146</v>
       </c>
-      <c r="AJ41" s="4" t="s">
+      <c r="AJ41" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK41" t="s">
@@ -6534,7 +6534,7 @@
       <c r="AI42" t="s">
         <v>81</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AJ42" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK42" t="s">
@@ -6557,7 +6557,7 @@
       </c>
     </row>
     <row r="43" spans="1:42">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B43">
@@ -6590,7 +6590,7 @@
       <c r="K43">
         <v>1.59</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43" s="6">
         <v>-1.1808952468956779</v>
       </c>
       <c r="M43">
@@ -6659,7 +6659,7 @@
       <c r="AI43" t="s">
         <v>150</v>
       </c>
-      <c r="AJ43" s="3" t="s">
+      <c r="AJ43" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK43" t="s">
@@ -6784,7 +6784,7 @@
       <c r="AI44" t="s">
         <v>81</v>
       </c>
-      <c r="AJ44" s="4" t="s">
+      <c r="AJ44" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK44" t="s">
@@ -6867,7 +6867,7 @@
       <c r="U45">
         <v>0</v>
       </c>
-      <c r="V45" s="2" t="b">
+      <c r="V45" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W45" t="b">
@@ -6909,7 +6909,7 @@
       <c r="AI45" t="s">
         <v>53</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AJ45" s="4" t="s">
         <v>156</v>
       </c>
       <c r="AK45" t="s">
@@ -6992,7 +6992,7 @@
       <c r="U46">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="b">
+      <c r="V46" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W46" t="b">
@@ -7034,7 +7034,7 @@
       <c r="AI46" t="s">
         <v>102</v>
       </c>
-      <c r="AJ46" s="4" t="s">
+      <c r="AJ46" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK46" t="s">
@@ -7057,7 +7057,7 @@
       </c>
     </row>
     <row r="47" spans="1:42">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B47">
@@ -7090,7 +7090,7 @@
       <c r="K47">
         <v>1.82</v>
       </c>
-      <c r="L47" s="5">
+      <c r="L47" s="6">
         <v>-1.0534184363637931</v>
       </c>
       <c r="M47">
@@ -7159,7 +7159,7 @@
       <c r="AI47" t="s">
         <v>120</v>
       </c>
-      <c r="AJ47" s="4" t="s">
+      <c r="AJ47" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK47" t="s">
@@ -7182,7 +7182,7 @@
       </c>
     </row>
     <row r="48" spans="1:42">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B48">
@@ -7242,7 +7242,7 @@
       <c r="U48">
         <v>12.22222222222222</v>
       </c>
-      <c r="V48" s="2" t="b">
+      <c r="V48" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="b">
@@ -7284,7 +7284,7 @@
       <c r="AI48" t="s">
         <v>161</v>
       </c>
-      <c r="AJ48" s="4" t="s">
+      <c r="AJ48" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK48" t="s">
@@ -7307,7 +7307,7 @@
       </c>
     </row>
     <row r="49" spans="1:42">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="7" t="s">
         <v>163</v>
       </c>
       <c r="B49">
@@ -7367,7 +7367,7 @@
       <c r="U49">
         <v>0</v>
       </c>
-      <c r="V49" s="2" t="b">
+      <c r="V49" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W49" t="b">
@@ -7409,7 +7409,7 @@
       <c r="AI49" t="s">
         <v>74</v>
       </c>
-      <c r="AJ49" s="4" t="s">
+      <c r="AJ49" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK49" t="s">
@@ -7492,7 +7492,7 @@
       <c r="U50">
         <v>4.4444444444444438</v>
       </c>
-      <c r="V50" s="2" t="b">
+      <c r="V50" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W50" t="b">
@@ -7534,7 +7534,7 @@
       <c r="AI50" t="s">
         <v>43</v>
       </c>
-      <c r="AJ50" s="4" t="s">
+      <c r="AJ50" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK50" t="s">
@@ -7557,7 +7557,7 @@
       </c>
     </row>
     <row r="51" spans="1:42">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B51">
@@ -7659,7 +7659,7 @@
       <c r="AI51" t="s">
         <v>44</v>
       </c>
-      <c r="AJ51" s="4" t="s">
+      <c r="AJ51" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK51" t="s">
@@ -7682,7 +7682,7 @@
       </c>
     </row>
     <row r="52" spans="1:42">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="9" t="s">
         <v>168</v>
       </c>
       <c r="B52">
@@ -7742,7 +7742,7 @@
       <c r="U52">
         <v>3.333333333333333</v>
       </c>
-      <c r="V52" s="2" t="b">
+      <c r="V52" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W52" t="b">
@@ -7781,7 +7781,7 @@
       <c r="AI52" t="s">
         <v>43</v>
       </c>
-      <c r="AJ52" s="4" t="s">
+      <c r="AJ52" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK52" t="s">
@@ -7906,7 +7906,7 @@
       <c r="AI53" t="s">
         <v>81</v>
       </c>
-      <c r="AJ53" s="4" t="s">
+      <c r="AJ53" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK53" t="s">
@@ -8031,7 +8031,7 @@
       <c r="AI54" t="s">
         <v>173</v>
       </c>
-      <c r="AJ54" s="4" t="s">
+      <c r="AJ54" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK54" t="s">
@@ -8156,7 +8156,7 @@
       <c r="AI55" t="s">
         <v>44</v>
       </c>
-      <c r="AJ55" s="3" t="s">
+      <c r="AJ55" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK55" t="s">
@@ -8179,7 +8179,7 @@
       </c>
     </row>
     <row r="56" spans="1:42">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="7" t="s">
         <v>175</v>
       </c>
       <c r="B56">
@@ -8281,7 +8281,7 @@
       <c r="AI56" t="s">
         <v>176</v>
       </c>
-      <c r="AJ56" s="3" t="s">
+      <c r="AJ56" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK56" t="s">
@@ -8364,7 +8364,7 @@
       <c r="U57">
         <v>12.77777777777778</v>
       </c>
-      <c r="V57" s="2" t="b">
+      <c r="V57" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W57" t="b">
@@ -8406,7 +8406,7 @@
       <c r="AI57" t="s">
         <v>84</v>
       </c>
-      <c r="AJ57" s="4" t="s">
+      <c r="AJ57" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK57" t="s">
@@ -8531,7 +8531,7 @@
       <c r="AI58" t="s">
         <v>180</v>
       </c>
-      <c r="AJ58" s="3" t="s">
+      <c r="AJ58" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK58" t="s">
@@ -8587,7 +8587,7 @@
       <c r="K59">
         <v>9.3800000000000008</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="7">
         <v>3.1366889011190349</v>
       </c>
       <c r="M59">
@@ -8656,7 +8656,7 @@
       <c r="AI59" t="s">
         <v>183</v>
       </c>
-      <c r="AJ59" s="3" t="s">
+      <c r="AJ59" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK59" t="s">
@@ -8781,7 +8781,7 @@
       <c r="AI60" t="s">
         <v>53</v>
       </c>
-      <c r="AJ60" s="3" t="s">
+      <c r="AJ60" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK60" t="s">
@@ -8831,13 +8831,13 @@
       <c r="I61">
         <v>9.94</v>
       </c>
-      <c r="J61" s="6">
+      <c r="J61" s="7">
         <v>3.0371669900490721</v>
       </c>
       <c r="K61">
         <v>8.64</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="7">
         <v>2.726546119407752</v>
       </c>
       <c r="M61">
@@ -8906,7 +8906,7 @@
       <c r="AI61" t="s">
         <v>84</v>
       </c>
-      <c r="AJ61" s="4" t="s">
+      <c r="AJ61" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK61" t="s">
@@ -8956,13 +8956,13 @@
       <c r="I62">
         <v>8.1300000000000008</v>
       </c>
-      <c r="J62" s="6">
+      <c r="J62" s="7">
         <v>2.2095099108668501</v>
       </c>
       <c r="K62">
         <v>8.02</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="7">
         <v>2.3829129779739748</v>
       </c>
       <c r="M62">
@@ -9031,7 +9031,7 @@
       <c r="AI62" t="s">
         <v>173</v>
       </c>
-      <c r="AJ62" s="3" t="s">
+      <c r="AJ62" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK62" t="s">
@@ -9081,13 +9081,13 @@
       <c r="I63">
         <v>0.16</v>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="6">
         <v>-1.434924852162053</v>
       </c>
       <c r="K63">
         <v>0.56000000000000005</v>
       </c>
-      <c r="L63" s="5">
+      <c r="L63" s="6">
         <v>-1.7517696592775971</v>
       </c>
       <c r="M63">
@@ -9114,7 +9114,7 @@
       <c r="U63">
         <v>2.7777777777777781</v>
       </c>
-      <c r="V63" s="2" t="b">
+      <c r="V63" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W63" t="b">
@@ -9156,7 +9156,7 @@
       <c r="AI63" t="s">
         <v>81</v>
       </c>
-      <c r="AJ63" s="4" t="s">
+      <c r="AJ63" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK63" t="s">
@@ -9179,7 +9179,7 @@
       </c>
     </row>
     <row r="64" spans="1:42">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="7" t="s">
         <v>191</v>
       </c>
       <c r="B64">
@@ -9278,7 +9278,7 @@
       <c r="AI64" t="s">
         <v>192</v>
       </c>
-      <c r="AJ64" s="3" t="s">
+      <c r="AJ64" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK64" t="s">
@@ -9301,7 +9301,7 @@
       </c>
     </row>
     <row r="65" spans="1:42">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="7" t="s">
         <v>194</v>
       </c>
       <c r="B65">
@@ -9403,7 +9403,7 @@
       <c r="AI65" t="s">
         <v>84</v>
       </c>
-      <c r="AJ65" s="3" t="s">
+      <c r="AJ65" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK65" t="s">
@@ -9528,7 +9528,7 @@
       <c r="AI66" t="s">
         <v>44</v>
       </c>
-      <c r="AJ66" s="4" t="s">
+      <c r="AJ66" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK66" t="s">
@@ -9650,7 +9650,7 @@
       <c r="AI67" t="s">
         <v>173</v>
       </c>
-      <c r="AJ67" s="4" t="s">
+      <c r="AJ67" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK67" t="s">
@@ -9673,7 +9673,7 @@
       </c>
     </row>
     <row r="68" spans="1:42">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="7" t="s">
         <v>200</v>
       </c>
       <c r="B68">
@@ -9733,7 +9733,7 @@
       <c r="U68">
         <v>0</v>
       </c>
-      <c r="V68" s="2" t="b">
+      <c r="V68" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W68" t="b">
@@ -9775,7 +9775,7 @@
       <c r="AI68" t="s">
         <v>56</v>
       </c>
-      <c r="AJ68" s="4" t="s">
+      <c r="AJ68" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK68" t="s">
@@ -9900,7 +9900,7 @@
       <c r="AI69" t="s">
         <v>173</v>
       </c>
-      <c r="AJ69" s="4" t="s">
+      <c r="AJ69" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK69" t="s">
@@ -9950,13 +9950,13 @@
       <c r="I70">
         <v>9.7799999999999994</v>
       </c>
-      <c r="J70" s="6">
+      <c r="J70" s="7">
         <v>2.964003933325781</v>
       </c>
       <c r="K70">
         <v>8.3000000000000007</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="7">
         <v>2.5381021386214879</v>
       </c>
       <c r="M70">
@@ -10028,7 +10028,7 @@
       <c r="AI70" t="s">
         <v>53</v>
       </c>
-      <c r="AJ70" s="4" t="s">
+      <c r="AJ70" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK70" t="s">
@@ -10153,7 +10153,7 @@
       <c r="AI71" t="s">
         <v>74</v>
       </c>
-      <c r="AJ71" s="3" t="s">
+      <c r="AJ71" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK71" t="s">
@@ -10203,13 +10203,13 @@
       <c r="I72">
         <v>0.17</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="6">
         <v>-1.4303521611168479</v>
       </c>
       <c r="K72">
         <v>0.35</v>
       </c>
-      <c r="L72" s="5">
+      <c r="L72" s="6">
         <v>-1.868161529763231</v>
       </c>
       <c r="M72">
@@ -10236,7 +10236,7 @@
       <c r="U72">
         <v>0</v>
       </c>
-      <c r="V72" s="2" t="b">
+      <c r="V72" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W72" t="b">
@@ -10278,7 +10278,7 @@
       <c r="AI72" t="s">
         <v>207</v>
       </c>
-      <c r="AJ72" s="4" t="s">
+      <c r="AJ72" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK72" t="s">
@@ -10403,7 +10403,7 @@
       <c r="AI73" t="s">
         <v>113</v>
       </c>
-      <c r="AJ73" s="3" t="s">
+      <c r="AJ73" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK73" t="s">
@@ -10426,7 +10426,7 @@
       </c>
     </row>
     <row r="74" spans="1:42">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="7" t="s">
         <v>209</v>
       </c>
       <c r="B74">
@@ -10528,7 +10528,7 @@
       <c r="AI74" t="s">
         <v>56</v>
       </c>
-      <c r="AJ74" s="4" t="s">
+      <c r="AJ74" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK74" t="s">
@@ -10653,7 +10653,7 @@
       <c r="AI75" t="s">
         <v>84</v>
       </c>
-      <c r="AJ75" s="3" t="s">
+      <c r="AJ75" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK75" t="s">
@@ -10733,7 +10733,7 @@
       <c r="S76">
         <v>1.22</v>
       </c>
-      <c r="T76" s="5" t="s">
+      <c r="T76" s="6" t="s">
         <v>19</v>
       </c>
       <c r="U76">
@@ -10781,7 +10781,7 @@
       <c r="AI76" t="s">
         <v>173</v>
       </c>
-      <c r="AJ76" s="4" t="s">
+      <c r="AJ76" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK76" t="s">
@@ -10804,7 +10804,7 @@
       </c>
     </row>
     <row r="77" spans="1:42">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="7" t="s">
         <v>213</v>
       </c>
       <c r="B77">
@@ -10837,7 +10837,7 @@
       <c r="K77">
         <v>1.82</v>
       </c>
-      <c r="L77" s="5">
+      <c r="L77" s="6">
         <v>-1.0534184363637931</v>
       </c>
       <c r="M77">
@@ -10864,7 +10864,7 @@
       <c r="U77">
         <v>1.1111111111111109</v>
       </c>
-      <c r="V77" s="2" t="b">
+      <c r="V77" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W77" t="b">
@@ -10903,7 +10903,7 @@
       <c r="AI77" t="s">
         <v>90</v>
       </c>
-      <c r="AJ77" s="4" t="s">
+      <c r="AJ77" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK77" t="s">
@@ -11028,7 +11028,7 @@
       <c r="AI78" t="s">
         <v>56</v>
       </c>
-      <c r="AJ78" s="4" t="s">
+      <c r="AJ78" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK78" t="s">
@@ -11153,7 +11153,7 @@
       <c r="AI79" t="s">
         <v>71</v>
       </c>
-      <c r="AJ79" s="3" t="s">
+      <c r="AJ79" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK79" t="s">
@@ -11236,7 +11236,7 @@
       <c r="U80">
         <v>5</v>
       </c>
-      <c r="V80" s="2" t="b">
+      <c r="V80" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W80" t="b">
@@ -11278,7 +11278,7 @@
       <c r="AI80" t="s">
         <v>81</v>
       </c>
-      <c r="AJ80" s="3" t="s">
+      <c r="AJ80" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK80" t="s">
@@ -11403,7 +11403,7 @@
       <c r="AI81" t="s">
         <v>102</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AJ81" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK81" t="s">
@@ -11483,7 +11483,7 @@
       <c r="S82">
         <v>1.24</v>
       </c>
-      <c r="T82" s="5" t="s">
+      <c r="T82" s="6" t="s">
         <v>19</v>
       </c>
       <c r="U82">
@@ -11531,7 +11531,7 @@
       <c r="AI82" t="s">
         <v>84</v>
       </c>
-      <c r="AJ82" s="4" t="s">
+      <c r="AJ82" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK82" t="s">
@@ -11653,7 +11653,7 @@
       <c r="AI83" t="s">
         <v>56</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AJ83" s="4" t="s">
         <v>156</v>
       </c>
       <c r="AK83" t="s">
@@ -11778,7 +11778,7 @@
       <c r="AI84" t="s">
         <v>53</v>
       </c>
-      <c r="AJ84" s="4" t="s">
+      <c r="AJ84" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK84" t="s">
@@ -11828,13 +11828,13 @@
       <c r="I85">
         <v>14.48</v>
       </c>
-      <c r="J85" s="6">
+      <c r="J85" s="7">
         <v>5.1131687245724367</v>
       </c>
       <c r="K85">
         <v>12.02</v>
       </c>
-      <c r="L85" s="6">
+      <c r="L85" s="7">
         <v>4.5999009872241494</v>
       </c>
       <c r="M85">
@@ -11903,7 +11903,7 @@
       <c r="AI85" t="s">
         <v>84</v>
       </c>
-      <c r="AJ85" s="4" t="s">
+      <c r="AJ85" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK85" t="s">
@@ -11986,7 +11986,7 @@
       <c r="U86">
         <v>14.444444444444439</v>
       </c>
-      <c r="V86" s="2" t="b">
+      <c r="V86" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W86" t="b">
@@ -12028,7 +12028,7 @@
       <c r="AI86" t="s">
         <v>44</v>
       </c>
-      <c r="AJ86" s="3" t="s">
+      <c r="AJ86" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK86" t="s">
@@ -12153,7 +12153,7 @@
       <c r="AI87" t="s">
         <v>230</v>
       </c>
-      <c r="AJ87" s="4" t="s">
+      <c r="AJ87" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK87" t="s">
@@ -12236,7 +12236,7 @@
       <c r="U88">
         <v>0</v>
       </c>
-      <c r="V88" s="2" t="b">
+      <c r="V88" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W88" t="b">
@@ -12278,7 +12278,7 @@
       <c r="AI88" t="s">
         <v>173</v>
       </c>
-      <c r="AJ88" s="4" t="s">
+      <c r="AJ88" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK88" t="s">
@@ -12361,7 +12361,7 @@
       <c r="U89">
         <v>3.333333333333333</v>
       </c>
-      <c r="V89" s="2" t="b">
+      <c r="V89" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W89" t="b">
@@ -12403,7 +12403,7 @@
       <c r="AI89" t="s">
         <v>53</v>
       </c>
-      <c r="AJ89" s="4" t="s">
+      <c r="AJ89" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK89" t="s">
@@ -12528,7 +12528,7 @@
       <c r="AI90" t="s">
         <v>74</v>
       </c>
-      <c r="AJ90" s="3" t="s">
+      <c r="AJ90" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK90" t="s">
@@ -12653,7 +12653,7 @@
       <c r="AI91" t="s">
         <v>183</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AJ91" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK91" t="s">
@@ -12778,7 +12778,7 @@
       <c r="AI92" t="s">
         <v>53</v>
       </c>
-      <c r="AJ92" s="3" t="s">
+      <c r="AJ92" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK92" t="s">
@@ -12861,7 +12861,7 @@
       <c r="U93">
         <v>2.2222222222222219</v>
       </c>
-      <c r="V93" s="2" t="b">
+      <c r="V93" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W93" t="b">
@@ -12903,7 +12903,7 @@
       <c r="AI93" t="s">
         <v>173</v>
       </c>
-      <c r="AJ93" s="4" t="s">
+      <c r="AJ93" s="5" t="s">
         <v>117</v>
       </c>
       <c r="AK93" t="s">
@@ -12926,7 +12926,7 @@
       </c>
     </row>
     <row r="94" spans="1:42">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="7" t="s">
         <v>240</v>
       </c>
       <c r="B94">
@@ -12986,7 +12986,7 @@
       <c r="U94">
         <v>0</v>
       </c>
-      <c r="V94" s="2" t="b">
+      <c r="V94" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W94" t="b">
@@ -13022,7 +13022,7 @@
       <c r="AI94" t="s">
         <v>84</v>
       </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AJ94" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK94" t="s">
@@ -13147,7 +13147,7 @@
       <c r="AI95" t="s">
         <v>74</v>
       </c>
-      <c r="AJ95" s="3" t="s">
+      <c r="AJ95" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK95" t="s">
@@ -13230,7 +13230,7 @@
       <c r="U96">
         <v>6.1111111111111107</v>
       </c>
-      <c r="V96" s="2" t="b">
+      <c r="V96" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W96" t="b">
@@ -13272,7 +13272,7 @@
       <c r="AI96" t="s">
         <v>44</v>
       </c>
-      <c r="AJ96" s="3" t="s">
+      <c r="AJ96" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK96" t="s">
@@ -13355,7 +13355,7 @@
       <c r="U97">
         <v>0</v>
       </c>
-      <c r="V97" s="2" t="b">
+      <c r="V97" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W97" t="b">
@@ -13397,7 +13397,7 @@
       <c r="AI97" t="s">
         <v>74</v>
       </c>
-      <c r="AJ97" s="3" t="s">
+      <c r="AJ97" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK97" t="s">
@@ -13522,7 +13522,7 @@
       <c r="AI98" t="s">
         <v>81</v>
       </c>
-      <c r="AJ98" s="3" t="s">
+      <c r="AJ98" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK98" t="s">
@@ -13647,7 +13647,7 @@
       <c r="AI99" t="s">
         <v>74</v>
       </c>
-      <c r="AJ99" s="3" t="s">
+      <c r="AJ99" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK99" t="s">
@@ -13730,7 +13730,7 @@
       <c r="U100">
         <v>0</v>
       </c>
-      <c r="V100" s="2" t="b">
+      <c r="V100" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W100" t="b">
@@ -13772,7 +13772,7 @@
       <c r="AI100" t="s">
         <v>81</v>
       </c>
-      <c r="AJ100" s="4" t="s">
+      <c r="AJ100" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK100" t="s">
@@ -13855,7 +13855,7 @@
       <c r="U101">
         <v>0</v>
       </c>
-      <c r="V101" s="2" t="b">
+      <c r="V101" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W101" t="b">
@@ -13897,7 +13897,7 @@
       <c r="AI101" t="s">
         <v>74</v>
       </c>
-      <c r="AJ101" s="4" t="s">
+      <c r="AJ101" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK101" t="s">
@@ -14022,7 +14022,7 @@
       <c r="AI102" t="s">
         <v>173</v>
       </c>
-      <c r="AJ102" s="4" t="s">
+      <c r="AJ102" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK102" t="s">
@@ -14105,7 +14105,7 @@
       <c r="U103">
         <v>1.1111111111111109</v>
       </c>
-      <c r="V103" s="2" t="b">
+      <c r="V103" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W103" t="b">
@@ -14147,7 +14147,7 @@
       <c r="AI103" t="s">
         <v>84</v>
       </c>
-      <c r="AJ103" s="3" t="s">
+      <c r="AJ103" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK103" t="s">
@@ -14170,7 +14170,7 @@
       </c>
     </row>
     <row r="104" spans="1:42">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="7" t="s">
         <v>251</v>
       </c>
       <c r="B104">
@@ -14272,7 +14272,7 @@
       <c r="AI104" t="s">
         <v>74</v>
       </c>
-      <c r="AJ104" s="3" t="s">
+      <c r="AJ104" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK104" t="s">
@@ -14397,7 +14397,7 @@
       <c r="AI105" t="s">
         <v>183</v>
       </c>
-      <c r="AJ105" s="3" t="s">
+      <c r="AJ105" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK105" t="s">
@@ -14522,7 +14522,7 @@
       <c r="AI106" t="s">
         <v>44</v>
       </c>
-      <c r="AJ106" s="4" t="s">
+      <c r="AJ106" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK106" t="s">
@@ -14545,7 +14545,7 @@
       </c>
     </row>
     <row r="107" spans="1:42">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="7" t="s">
         <v>255</v>
       </c>
       <c r="B107">
@@ -14605,7 +14605,7 @@
       <c r="U107">
         <v>0</v>
       </c>
-      <c r="V107" s="2" t="b">
+      <c r="V107" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W107" t="b">
@@ -14647,7 +14647,7 @@
       <c r="AI107" t="s">
         <v>90</v>
       </c>
-      <c r="AJ107" s="4" t="s">
+      <c r="AJ107" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK107" t="s">
@@ -14670,7 +14670,7 @@
       </c>
     </row>
     <row r="108" spans="1:42">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="7" t="s">
         <v>256</v>
       </c>
       <c r="B108">
@@ -14730,7 +14730,7 @@
       <c r="U108">
         <v>0</v>
       </c>
-      <c r="V108" s="2" t="b">
+      <c r="V108" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W108" t="b">
@@ -14772,7 +14772,7 @@
       <c r="AI108" t="s">
         <v>257</v>
       </c>
-      <c r="AJ108" s="4" t="s">
+      <c r="AJ108" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK108" t="s">
@@ -14855,7 +14855,7 @@
       <c r="U109">
         <v>0</v>
       </c>
-      <c r="V109" s="2" t="b">
+      <c r="V109" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W109" t="b">
@@ -14897,7 +14897,7 @@
       <c r="AI109" t="s">
         <v>67</v>
       </c>
-      <c r="AJ109" s="4" t="s">
+      <c r="AJ109" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK109" t="s">
@@ -14920,7 +14920,7 @@
       </c>
     </row>
     <row r="110" spans="1:42">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="7" t="s">
         <v>259</v>
       </c>
       <c r="B110">
@@ -15022,7 +15022,7 @@
       <c r="AI110" t="s">
         <v>81</v>
       </c>
-      <c r="AJ110" s="4" t="s">
+      <c r="AJ110" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK110" t="s">
@@ -15147,7 +15147,7 @@
       <c r="AI111" t="s">
         <v>43</v>
       </c>
-      <c r="AJ111" s="4" t="s">
+      <c r="AJ111" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK111" t="s">
@@ -15197,7 +15197,7 @@
       <c r="I112">
         <v>8.44</v>
       </c>
-      <c r="J112" s="6">
+      <c r="J112" s="7">
         <v>2.351263333268224</v>
       </c>
       <c r="K112">
@@ -15272,7 +15272,7 @@
       <c r="AI112" t="s">
         <v>44</v>
       </c>
-      <c r="AJ112" s="3" t="s">
+      <c r="AJ112" s="4" t="s">
         <v>75</v>
       </c>
       <c r="AK112" t="s">
@@ -15400,7 +15400,7 @@
       <c r="AI113" t="s">
         <v>81</v>
       </c>
-      <c r="AJ113" s="4" t="s">
+      <c r="AJ113" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK113" t="s">
@@ -15423,7 +15423,7 @@
       </c>
     </row>
     <row r="114" spans="1:42">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="7" t="s">
         <v>264</v>
       </c>
       <c r="B114">
@@ -15525,7 +15525,7 @@
       <c r="AI114" t="s">
         <v>257</v>
       </c>
-      <c r="AJ114" s="3" t="s">
+      <c r="AJ114" s="4" t="s">
         <v>156</v>
       </c>
       <c r="AK114" t="s">
@@ -15581,7 +15581,7 @@
       <c r="K115">
         <v>10.5</v>
       </c>
-      <c r="L115" s="6">
+      <c r="L115" s="7">
         <v>3.7574455437090828</v>
       </c>
       <c r="M115">
@@ -15650,7 +15650,7 @@
       <c r="AI115" t="s">
         <v>90</v>
       </c>
-      <c r="AJ115" s="3" t="s">
+      <c r="AJ115" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK115" t="s">
@@ -15775,7 +15775,7 @@
       <c r="AI116" t="s">
         <v>81</v>
       </c>
-      <c r="AJ116" s="4" t="s">
+      <c r="AJ116" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK116" t="s">
@@ -15858,7 +15858,7 @@
       <c r="U117">
         <v>0</v>
       </c>
-      <c r="V117" s="2" t="b">
+      <c r="V117" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W117" t="b">
@@ -15900,7 +15900,7 @@
       <c r="AI117" t="s">
         <v>102</v>
       </c>
-      <c r="AJ117" s="4" t="s">
+      <c r="AJ117" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK117" t="s">
@@ -15983,7 +15983,7 @@
       <c r="U118">
         <v>0</v>
       </c>
-      <c r="V118" s="2" t="b">
+      <c r="V118" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W118" t="b">
@@ -16025,7 +16025,7 @@
       <c r="AI118" t="s">
         <v>84</v>
       </c>
-      <c r="AJ118" s="3" t="s">
+      <c r="AJ118" s="4" t="s">
         <v>64</v>
       </c>
       <c r="AK118" t="s">
@@ -16048,7 +16048,7 @@
       </c>
     </row>
     <row r="119" spans="1:42">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="7" t="s">
         <v>275</v>
       </c>
       <c r="B119">
@@ -16150,7 +16150,7 @@
       <c r="AI119" t="s">
         <v>192</v>
       </c>
-      <c r="AJ119" s="4" t="s">
+      <c r="AJ119" s="5" t="s">
         <v>68</v>
       </c>
       <c r="AK119" t="s">
@@ -16173,7 +16173,7 @@
       </c>
     </row>
     <row r="120" spans="1:42">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="7" t="s">
         <v>276</v>
       </c>
       <c r="B120">
@@ -16275,7 +16275,7 @@
       <c r="AI120" t="s">
         <v>74</v>
       </c>
-      <c r="AJ120" s="4" t="s">
+      <c r="AJ120" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK120" t="s">
@@ -16400,7 +16400,7 @@
       <c r="AI121" t="s">
         <v>81</v>
       </c>
-      <c r="AJ121" s="4" t="s">
+      <c r="AJ121" s="5" t="s">
         <v>50</v>
       </c>
       <c r="AK121" t="s">
@@ -16483,7 +16483,7 @@
       <c r="U122">
         <v>9.4444444444444429</v>
       </c>
-      <c r="V122" s="2" t="b">
+      <c r="V122" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W122" t="b">
@@ -16525,7 +16525,7 @@
       <c r="AI122" t="s">
         <v>150</v>
       </c>
-      <c r="AJ122" s="4" t="s">
+      <c r="AJ122" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK122" t="s">
@@ -16650,7 +16650,7 @@
       <c r="AI123" t="s">
         <v>74</v>
       </c>
-      <c r="AJ123" s="3" t="s">
+      <c r="AJ123" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK123" t="s">
@@ -16673,7 +16673,7 @@
       </c>
     </row>
     <row r="124" spans="1:42">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="7" t="s">
         <v>280</v>
       </c>
       <c r="B124">
@@ -16733,7 +16733,7 @@
       <c r="U124">
         <v>0</v>
       </c>
-      <c r="V124" s="2" t="b">
+      <c r="V124" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W124" t="b">
@@ -16775,7 +16775,7 @@
       <c r="AI124" t="s">
         <v>150</v>
       </c>
-      <c r="AJ124" s="4" t="s">
+      <c r="AJ124" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK124" t="s">
@@ -16858,7 +16858,7 @@
       <c r="U125">
         <v>0</v>
       </c>
-      <c r="V125" s="2" t="b">
+      <c r="V125" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W125" t="b">
@@ -16900,7 +16900,7 @@
       <c r="AI125" t="s">
         <v>84</v>
       </c>
-      <c r="AJ125" s="4" t="s">
+      <c r="AJ125" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK125" t="s">
@@ -16983,7 +16983,7 @@
       <c r="U126">
         <v>0.55555555555555547</v>
       </c>
-      <c r="V126" s="2" t="b">
+      <c r="V126" s="3" t="b">
         <v>1</v>
       </c>
       <c r="W126" t="b">
@@ -17025,7 +17025,7 @@
       <c r="AI126" t="s">
         <v>161</v>
       </c>
-      <c r="AJ126" s="4" t="s">
+      <c r="AJ126" s="5" t="s">
         <v>121</v>
       </c>
       <c r="AK126" t="s">
@@ -17048,7 +17048,7 @@
       </c>
     </row>
     <row r="127" spans="1:42">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="7" t="s">
         <v>283</v>
       </c>
       <c r="B127">
@@ -17075,7 +17075,7 @@
       <c r="I127">
         <v>7.8</v>
       </c>
-      <c r="J127" s="6">
+      <c r="J127" s="7">
         <v>2.0586111063750629</v>
       </c>
       <c r="K127">
@@ -17150,7 +17150,7 @@
       <c r="AI127" t="s">
         <v>173</v>
       </c>
-      <c r="AJ127" s="3" t="s">
+      <c r="AJ127" s="4" t="s">
         <v>104</v>
       </c>
       <c r="AK127" t="s">
@@ -17173,7 +17173,7 @@
       </c>
     </row>
     <row r="128" spans="1:42">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="7" t="s">
         <v>284</v>
       </c>
       <c r="B128">
@@ -17275,7 +17275,7 @@
       <c r="AI128" t="s">
         <v>44</v>
       </c>
-      <c r="AJ128" s="3" t="s">
+      <c r="AJ128" s="4" t="s">
         <v>45</v>
       </c>
       <c r="AK128" t="s">
@@ -17298,7 +17298,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>